--- a/MiningSystemDRS_ConfExStrings_v4.xlsx
+++ b/MiningSystemDRS_ConfExStrings_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anavarra\Desktop\Practice DRS Construction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Desktop\School\2026W\COMP 396\Mining-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15031B6-8F2E-4098-B606-ED7DF8C3D6E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552E7261-269C-4552-AF86-CA01A591F6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33750" yWindow="1260" windowWidth="15540" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2592" yWindow="300" windowWidth="22272" windowHeight="12228" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,15 +200,6 @@
     <t>TimeInShutdown_Level</t>
   </si>
   <si>
-    <t>ore mass in parcel</t>
-  </si>
-  <si>
-    <t>% of Ore Type 2</t>
-  </si>
-  <si>
-    <t>NextParcelIsNewFacie</t>
-  </si>
-  <si>
     <t>"30"</t>
   </si>
   <si>
@@ -501,6 +492,15 @@
   </si>
   <si>
     <t>confExString_AssignmentSequence  (Prefix "L" = Level,  "T" = Timer, "N" = Discretely Dynamical Numerical, "C" = Categorical, "E" = Run External Code)</t>
+  </si>
+  <si>
+    <t>MassOfCurrentParcel</t>
+  </si>
+  <si>
+    <t>PercentageOfOre2InCurrentParcel</t>
+  </si>
+  <si>
+    <t>NextParcelIsNewFacies</t>
   </si>
 </sst>
 </file>
@@ -637,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -646,9 +646,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -663,17 +660,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -964,21 +952,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I242"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:I242"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" style="3" customWidth="1"/>
-    <col min="5" max="9" width="36.5703125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="16.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" style="3" customWidth="1"/>
+    <col min="5" max="9" width="36.5546875" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
@@ -986,24 +971,24 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1014,7 +999,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1010,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1036,7 +1021,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1047,7 +1032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
@@ -1058,12 +1043,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1071,7 +1056,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
@@ -1079,7 +1064,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
@@ -1087,7 +1072,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
@@ -1095,7 +1080,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>50</v>
       </c>
@@ -1103,7 +1088,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
@@ -1111,7 +1096,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>52</v>
       </c>
@@ -1119,7 +1104,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>53</v>
       </c>
@@ -1127,7 +1112,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>54</v>
       </c>
@@ -1135,58 +1120,51 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C35" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C35" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G37" s="4"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G38" s="4"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C39" s="3" t="s">
         <v>5</v>
       </c>
@@ -1209,59 +1187,59 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="I40" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="H41" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="I41" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>2</v>
       </c>
@@ -1272,7 +1250,7 @@
         <v>42</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>42</v>
@@ -1281,57 +1259,57 @@
         <v>42</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="I43" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="H44" s="2" t="s">
         <v>42</v>
       </c>
@@ -1339,19 +1317,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C48" s="3" t="s">
         <v>5</v>
       </c>
@@ -1374,85 +1345,85 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
@@ -1463,22 +1434,22 @@
         <v>42</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>4</v>
       </c>
@@ -1486,10 +1457,10 @@
         <v>42</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>42</v>
@@ -1498,24 +1469,18 @@
         <v>42</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G54" s="4"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G55" s="4"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C57" s="3" t="s">
         <v>5</v>
       </c>
@@ -1538,142 +1503,142 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C66" s="3" t="s">
         <v>5</v>
       </c>
@@ -1696,7 +1661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>0</v>
       </c>
@@ -1722,7 +1687,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
         <v>1</v>
       </c>
@@ -1748,7 +1713,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
         <v>2</v>
       </c>
@@ -1759,7 +1724,7 @@
         <v>42</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>42</v>
@@ -1768,27 +1733,27 @@
         <v>42</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>42</v>
@@ -1800,12 +1765,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>42</v>
@@ -1814,10 +1779,10 @@
         <v>42</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>42</v>
@@ -1826,12 +1791,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C75" s="3" t="s">
         <v>5</v>
       </c>
@@ -1854,59 +1819,59 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E76" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H76" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="I76" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E77" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="I77" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
         <v>2</v>
       </c>
@@ -1932,7 +1897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
         <v>3</v>
       </c>
@@ -1958,7 +1923,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>4</v>
       </c>
@@ -1984,12 +1949,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C84" s="3" t="s">
         <v>5</v>
       </c>
@@ -2012,7 +1977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>0</v>
       </c>
@@ -2038,7 +2003,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>1</v>
       </c>
@@ -2064,7 +2029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
         <v>2</v>
       </c>
@@ -2090,7 +2055,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>3</v>
       </c>
@@ -2104,7 +2069,7 @@
         <v>42</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>42</v>
@@ -2116,12 +2081,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>42</v>
@@ -2142,12 +2107,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C93" s="3" t="s">
         <v>5</v>
       </c>
@@ -2170,59 +2135,59 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
         <v>2</v>
       </c>
@@ -2248,7 +2213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
         <v>3</v>
       </c>
@@ -2274,7 +2239,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
         <v>4</v>
       </c>
@@ -2300,19 +2265,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C102" s="3" t="s">
         <v>5</v>
       </c>
@@ -2335,33 +2300,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
         <v>13</v>
       </c>
@@ -2369,7 +2334,7 @@
         <v>42</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>42</v>
@@ -2378,7 +2343,7 @@
         <v>42</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>42</v>
@@ -2387,12 +2352,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>42</v>
@@ -2413,7 +2378,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
         <v>15</v>
       </c>
@@ -2421,7 +2386,7 @@
         <v>42</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>42</v>
@@ -2439,7 +2404,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
         <v>16</v>
       </c>
@@ -2450,7 +2415,7 @@
         <v>42</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>42</v>
@@ -2465,7 +2430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
         <v>17</v>
       </c>
@@ -2479,7 +2444,7 @@
         <v>42</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>42</v>
@@ -2491,7 +2456,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
         <v>18</v>
       </c>
@@ -2508,7 +2473,7 @@
         <v>42</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>42</v>
@@ -2517,7 +2482,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
         <v>19</v>
       </c>
@@ -2537,13 +2502,13 @@
         <v>42</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
         <v>20</v>
       </c>
@@ -2566,15 +2531,15 @@
         <v>42</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C115" s="3" t="s">
         <v>5</v>
       </c>
@@ -2597,246 +2562,246 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B118" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B123" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C128" s="3" t="s">
         <v>5</v>
       </c>
@@ -2859,246 +2824,246 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C141" s="3" t="s">
         <v>5</v>
       </c>
@@ -3121,7 +3086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B142" s="1" t="s">
         <v>12</v>
       </c>
@@ -3147,7 +3112,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
         <v>13</v>
       </c>
@@ -3173,7 +3138,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
         <v>14</v>
       </c>
@@ -3199,7 +3164,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
         <v>15</v>
       </c>
@@ -3225,7 +3190,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
         <v>16</v>
       </c>
@@ -3251,7 +3216,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
         <v>17</v>
       </c>
@@ -3277,7 +3242,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
         <v>18</v>
       </c>
@@ -3303,7 +3268,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
         <v>19</v>
       </c>
@@ -3329,7 +3294,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
         <v>20</v>
       </c>
@@ -3355,12 +3320,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C154" s="3" t="s">
         <v>5</v>
       </c>
@@ -3383,33 +3348,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
         <v>13</v>
       </c>
@@ -3417,7 +3382,7 @@
         <v>42</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>42</v>
@@ -3426,7 +3391,7 @@
         <v>42</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>42</v>
@@ -3435,7 +3400,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
         <v>14</v>
       </c>
@@ -3461,7 +3426,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
         <v>15</v>
       </c>
@@ -3487,7 +3452,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
         <v>16</v>
       </c>
@@ -3513,7 +3478,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
         <v>17</v>
       </c>
@@ -3539,7 +3504,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
         <v>18</v>
       </c>
@@ -3565,7 +3530,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
         <v>19</v>
       </c>
@@ -3591,7 +3556,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
         <v>20</v>
       </c>
@@ -3617,12 +3582,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C167" s="3" t="s">
         <v>5</v>
       </c>
@@ -3645,7 +3610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
         <v>12</v>
       </c>
@@ -3671,7 +3636,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B169" s="1" t="s">
         <v>13</v>
       </c>
@@ -3697,7 +3662,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B170" s="1" t="s">
         <v>14</v>
       </c>
@@ -3723,7 +3688,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B171" s="1" t="s">
         <v>15</v>
       </c>
@@ -3749,7 +3714,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B172" s="1" t="s">
         <v>16</v>
       </c>
@@ -3775,7 +3740,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B173" s="1" t="s">
         <v>17</v>
       </c>
@@ -3801,7 +3766,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B174" s="1" t="s">
         <v>18</v>
       </c>
@@ -3827,7 +3792,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B175" s="1" t="s">
         <v>19</v>
       </c>
@@ -3853,7 +3818,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B176" s="1" t="s">
         <v>20</v>
       </c>
@@ -3879,12 +3844,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C180" s="3" t="s">
         <v>5</v>
       </c>
@@ -3907,33 +3872,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B181" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B182" s="1" t="s">
         <v>13</v>
       </c>
@@ -3959,7 +3924,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B183" s="1" t="s">
         <v>14</v>
       </c>
@@ -3985,7 +3950,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B184" s="1" t="s">
         <v>15</v>
       </c>
@@ -4011,7 +3976,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B185" s="1" t="s">
         <v>16</v>
       </c>
@@ -4037,7 +4002,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B186" s="1" t="s">
         <v>17</v>
       </c>
@@ -4063,7 +4028,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B187" s="1" t="s">
         <v>18</v>
       </c>
@@ -4089,7 +4054,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B188" s="1" t="s">
         <v>19</v>
       </c>
@@ -4115,7 +4080,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B189" s="1" t="s">
         <v>20</v>
       </c>
@@ -4141,627 +4106,504 @@
         <v>42</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C193" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F193" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D193" s="3" t="s">
+      <c r="G193" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E193" s="3" t="s">
+      <c r="H193" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F193" s="3" t="s">
+      <c r="I193" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G193" s="3" t="s">
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B194" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I194" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B195" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B196" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I196" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B197" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B198" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I198" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B199" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I199" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B202" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C202" s="5"/>
+      <c r="D202" s="5"/>
+      <c r="E202" s="5"/>
+      <c r="F202" s="5"/>
+      <c r="G202" s="6"/>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B203" s="7"/>
+      <c r="G203" s="8"/>
+    </row>
+    <row r="204" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B204" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G204" s="8"/>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B205" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H193" s="3" t="s">
+      <c r="C205" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G205" s="8"/>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B206" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I193" s="3" t="s">
+      <c r="C206" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G206" s="8"/>
+    </row>
+    <row r="207" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B207" s="7" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B194" s="1" t="s">
+      <c r="C207" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G207" s="8"/>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B208" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G208" s="8"/>
+    </row>
+    <row r="209" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B209" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G209" s="8"/>
+    </row>
+    <row r="210" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B210" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G210" s="8"/>
+    </row>
+    <row r="211" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B211" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G211" s="8"/>
+    </row>
+    <row r="212" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B212" s="7"/>
+      <c r="G212" s="8"/>
+    </row>
+    <row r="213" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B213" s="7"/>
+      <c r="G213" s="8"/>
+    </row>
+    <row r="214" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B214" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G214" s="8"/>
+    </row>
+    <row r="215" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B215" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G215" s="8"/>
+    </row>
+    <row r="216" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B216" s="7"/>
+      <c r="G216" s="8"/>
+    </row>
+    <row r="217" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B217" s="7"/>
+      <c r="F217" s="1"/>
+      <c r="G217" s="8"/>
+    </row>
+    <row r="218" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B218" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F218" s="1"/>
+      <c r="G218" s="8"/>
+    </row>
+    <row r="219" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B219" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F219" s="1"/>
+      <c r="G219" s="8"/>
+    </row>
+    <row r="220" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B220" s="7"/>
+      <c r="F220" s="1"/>
+      <c r="G220" s="8"/>
+    </row>
+    <row r="221" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B221" s="7"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="8"/>
+    </row>
+    <row r="222" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B222" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C194" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G194" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H194" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I194" s="2" t="s">
+      <c r="C222" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F222" s="1"/>
+      <c r="G222" s="8"/>
+    </row>
+    <row r="223" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B223" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C223" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B195" s="1" t="s">
+      <c r="G223" s="8"/>
+    </row>
+    <row r="224" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B224" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G224" s="8"/>
+    </row>
+    <row r="225" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B225" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G225" s="8"/>
+    </row>
+    <row r="226" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B226" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G226" s="8"/>
+    </row>
+    <row r="227" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B227" s="7"/>
+      <c r="G227" s="8"/>
+    </row>
+    <row r="228" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B228" s="7"/>
+      <c r="G228" s="8"/>
+    </row>
+    <row r="229" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B229" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C229" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G229" s="8"/>
+    </row>
+    <row r="230" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B230" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G230" s="8"/>
+    </row>
+    <row r="231" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B231" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C231" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D195" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H195" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I195" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B196" s="1" t="s">
+      <c r="G231" s="8"/>
+    </row>
+    <row r="232" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B232" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G232" s="8"/>
+    </row>
+    <row r="233" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B233" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G233" s="8"/>
+    </row>
+    <row r="234" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B234" s="7"/>
+      <c r="G234" s="8"/>
+    </row>
+    <row r="235" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B235" s="7"/>
+      <c r="G235" s="8"/>
+    </row>
+    <row r="236" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B236" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I196" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B197" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C197" s="2" t="s">
+      <c r="C236" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G236" s="8"/>
+    </row>
+    <row r="237" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B237" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G237" s="8"/>
+    </row>
+    <row r="238" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B238" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G238" s="8"/>
+    </row>
+    <row r="239" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B239" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G239" s="8"/>
+    </row>
+    <row r="240" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B240" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C240" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H197" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I197" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B198" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G198" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H198" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I198" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B199" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H199" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I199" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B202" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
-      <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
-      <c r="G202" s="7"/>
-    </row>
-    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B203" s="8"/>
-      <c r="C203" s="9"/>
-      <c r="D203" s="9"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="9"/>
-      <c r="G203" s="10"/>
-    </row>
-    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B204" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C204" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D204" s="9"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9"/>
-      <c r="G204" s="10"/>
-    </row>
-    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B205" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C205" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D205" s="9"/>
-      <c r="E205" s="9"/>
-      <c r="F205" s="9"/>
-      <c r="G205" s="10"/>
-    </row>
-    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B206" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C206" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D206" s="9"/>
-      <c r="E206" s="9"/>
-      <c r="F206" s="9"/>
-      <c r="G206" s="10"/>
-    </row>
-    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B207" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C207" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D207" s="9"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="9"/>
-      <c r="G207" s="10"/>
-    </row>
-    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B208" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C208" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D208" s="9"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="9"/>
-      <c r="G208" s="10"/>
-    </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B209" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C209" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D209" s="9"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="9"/>
-      <c r="G209" s="10"/>
-    </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B210" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="C210" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="9"/>
-      <c r="G210" s="10"/>
-    </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B211" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C211" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D211" s="9"/>
-      <c r="E211" s="9"/>
-      <c r="F211" s="9"/>
-      <c r="G211" s="10"/>
-    </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B212" s="8"/>
-      <c r="C212" s="11"/>
-      <c r="D212" s="9"/>
-      <c r="E212" s="9"/>
-      <c r="F212" s="9"/>
-      <c r="G212" s="10"/>
-    </row>
-    <row r="213" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B213" s="8"/>
-      <c r="C213" s="11"/>
-      <c r="D213" s="9"/>
-      <c r="E213" s="9"/>
-      <c r="F213" s="9"/>
-      <c r="G213" s="10"/>
-    </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B214" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C214" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D214" s="9"/>
-      <c r="E214" s="9"/>
-      <c r="F214" s="9"/>
-      <c r="G214" s="10"/>
-    </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B215" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C215" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D215" s="9"/>
-      <c r="E215" s="9"/>
-      <c r="F215" s="9"/>
-      <c r="G215" s="10"/>
-    </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B216" s="8"/>
-      <c r="C216" s="11"/>
-      <c r="D216" s="9"/>
-      <c r="E216" s="9"/>
-      <c r="F216" s="9"/>
-      <c r="G216" s="10"/>
-    </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B217" s="8"/>
-      <c r="C217" s="11"/>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="12"/>
-      <c r="G217" s="10"/>
-    </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B218" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C218" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="12"/>
-      <c r="G218" s="10"/>
-    </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B219" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C219" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D219" s="9"/>
-      <c r="E219" s="9"/>
-      <c r="F219" s="12"/>
-      <c r="G219" s="10"/>
-    </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B220" s="8"/>
-      <c r="C220" s="11"/>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
-      <c r="F220" s="12"/>
-      <c r="G220" s="10"/>
-    </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B221" s="8"/>
-      <c r="C221" s="11"/>
-      <c r="D221" s="9"/>
-      <c r="E221" s="9"/>
-      <c r="F221" s="12"/>
-      <c r="G221" s="10"/>
-    </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B222" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C222" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="12"/>
-      <c r="G222" s="10"/>
-    </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B223" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C223" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D223" s="9"/>
-      <c r="E223" s="9"/>
-      <c r="F223" s="9"/>
-      <c r="G223" s="10"/>
-    </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B224" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C224" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D224" s="9"/>
-      <c r="E224" s="9"/>
-      <c r="F224" s="9"/>
-      <c r="G224" s="10"/>
-    </row>
-    <row r="225" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B225" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C225" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D225" s="9"/>
-      <c r="E225" s="9"/>
-      <c r="F225" s="9"/>
-      <c r="G225" s="10"/>
-    </row>
-    <row r="226" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B226" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C226" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D226" s="9"/>
-      <c r="E226" s="9"/>
-      <c r="F226" s="9"/>
-      <c r="G226" s="10"/>
-    </row>
-    <row r="227" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B227" s="8"/>
-      <c r="C227" s="11"/>
-      <c r="D227" s="9"/>
-      <c r="E227" s="9"/>
-      <c r="F227" s="9"/>
-      <c r="G227" s="10"/>
-    </row>
-    <row r="228" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B228" s="8"/>
-      <c r="C228" s="11"/>
-      <c r="D228" s="9"/>
-      <c r="E228" s="9"/>
-      <c r="F228" s="9"/>
-      <c r="G228" s="10"/>
-    </row>
-    <row r="229" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B229" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C229" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D229" s="9"/>
-      <c r="E229" s="9"/>
-      <c r="F229" s="9"/>
-      <c r="G229" s="10"/>
-    </row>
-    <row r="230" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B230" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C230" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D230" s="9"/>
-      <c r="E230" s="9"/>
-      <c r="F230" s="9"/>
-      <c r="G230" s="10"/>
-    </row>
-    <row r="231" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B231" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C231" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D231" s="9"/>
-      <c r="E231" s="9"/>
-      <c r="F231" s="9"/>
-      <c r="G231" s="10"/>
-    </row>
-    <row r="232" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B232" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C232" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D232" s="9"/>
-      <c r="E232" s="9"/>
-      <c r="F232" s="9"/>
-      <c r="G232" s="10"/>
-    </row>
-    <row r="233" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B233" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C233" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D233" s="9"/>
-      <c r="E233" s="9"/>
-      <c r="F233" s="9"/>
-      <c r="G233" s="10"/>
-    </row>
-    <row r="234" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B234" s="8"/>
-      <c r="C234" s="11"/>
-      <c r="D234" s="9"/>
-      <c r="E234" s="9"/>
-      <c r="F234" s="9"/>
-      <c r="G234" s="10"/>
-    </row>
-    <row r="235" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B235" s="8"/>
-      <c r="C235" s="11"/>
-      <c r="D235" s="9"/>
-      <c r="E235" s="9"/>
-      <c r="F235" s="9"/>
-      <c r="G235" s="10"/>
-    </row>
-    <row r="236" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B236" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C236" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D236" s="9"/>
-      <c r="E236" s="9"/>
-      <c r="F236" s="9"/>
-      <c r="G236" s="10"/>
-    </row>
-    <row r="237" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B237" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C237" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="F237" s="9"/>
-      <c r="G237" s="10"/>
-    </row>
-    <row r="238" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B238" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C238" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D238" s="9"/>
-      <c r="E238" s="9"/>
-      <c r="F238" s="9"/>
-      <c r="G238" s="10"/>
-    </row>
-    <row r="239" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B239" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C239" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D239" s="9"/>
-      <c r="E239" s="9"/>
-      <c r="F239" s="9"/>
-      <c r="G239" s="10"/>
-    </row>
-    <row r="240" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B240" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C240" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D240" s="9"/>
-      <c r="E240" s="9"/>
-      <c r="F240" s="9"/>
-      <c r="G240" s="10"/>
-    </row>
-    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B241" s="8"/>
-      <c r="C241" s="9"/>
-      <c r="D241" s="9"/>
-      <c r="E241" s="9"/>
-      <c r="F241" s="9"/>
-      <c r="G241" s="10"/>
-    </row>
-    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B242" s="13"/>
-      <c r="C242" s="14"/>
-      <c r="D242" s="14"/>
-      <c r="E242" s="14"/>
-      <c r="F242" s="14"/>
-      <c r="G242" s="15"/>
+      <c r="G240" s="8"/>
+    </row>
+    <row r="241" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B241" s="7"/>
+      <c r="G241" s="8"/>
+    </row>
+    <row r="242" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B242" s="9"/>
+      <c r="C242" s="10"/>
+      <c r="D242" s="10"/>
+      <c r="E242" s="10"/>
+      <c r="F242" s="10"/>
+      <c r="G242" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
